--- a/data/trans_dic/IP31KM08_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,53; 62,3</t>
+          <t>36,18; 59,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,74; 59,29</t>
+          <t>46,94; 71,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,64; 56,49</t>
+          <t>44,37; 61,75</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,18; 48,86</t>
+          <t>40,33; 49,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,96; 49,23</t>
+          <t>43,2; 51,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,78; 47,81</t>
+          <t>43,57; 49,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 46,01</t>
+          <t>38,7; 51,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,87; 52,05</t>
+          <t>32,42; 46,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,1; 47,02</t>
+          <t>38,03; 47,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,78; 46,74</t>
+          <t>42,18; 49,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,04; 48,56</t>
+          <t>42,91; 49,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 46,72</t>
+          <t>43,43; 48,59</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27088</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>52964</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16392; 33456</t>
+          <t>19437; 31811</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20271; 34594</t>
+          <t>21546; 32611</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41051; 63296</t>
+          <t>44203; 61518</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>199276</t>
+          <t>212460</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>225352</t>
+          <t>201983</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424627</t>
+          <t>414444</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>158962; 220766</t>
+          <t>188088; 230217</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>201881; 248744</t>
+          <t>183463; 218489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>380761; 457554</t>
+          <t>388238; 444656</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>57527</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137659</t>
+          <t>133316</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46120; 67254</t>
+          <t>64509; 86295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68599; 94283</t>
+          <t>47698; 69086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121422; 153919</t>
+          <t>119359; 149925</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>405</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>280672</t>
+          <t>314265</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286459</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614448</t>
+          <t>600724</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>239715; 304589</t>
+          <t>289722; 339438</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>305651; 361634</t>
+          <t>265055; 307741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570318; 652419</t>
+          <t>566496; 633926</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM08_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman pasta o arroz casi a diario (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>48,43%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>58,71%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>36,18; 59,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>46,94; 71,04</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44,37; 61,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47,56%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>40,33; 49,36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43,2; 51,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43,57; 49,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39,1%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>38,7; 51,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>32,42; 46,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>38,03; 47,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>45,76%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46,37%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>42,18; 49,42</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42,91; 49,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43,43; 48,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4843140617511668</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5870627172526525</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.531660759209966</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>26015</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>26949</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52964</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3618488317394135</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.469357035666885</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4437142549265209</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19437; 31811</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21546; 32611</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>44203; 61518</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5922166056338637</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7103948326433486</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6175271308690229</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4555100989558684</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4756286688271781</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4650980004370017</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>212460</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>201983</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>414444</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4032563931218068</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4320176705027047</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4356891422272455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>188088; 230217</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>183463; 218489</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>388238; 444656</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.493580886011991</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5144954806450834</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4990020679327626</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4546857139067618</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3909670095746209</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4248106466057329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>75790</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>57527</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>133316</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3870110789026361</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3241645359883089</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3803355114619374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>64509; 86295</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>47698; 69086</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>119359; 149925</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5177071404644024</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4695279886044266</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4777355973224777</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4575627130454269</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4637432765973231</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4604892752137743</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>314265</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>286459</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>600724</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.421827956503055</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4290915702887723</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4342509362164633</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>289722; 339438</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>265055; 307741</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>566496; 633926</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4942146041384561</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4981965541501319</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4859402700547292</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman pasta o arroz casi a diario (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>26015</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>26949</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>52964</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>19437</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>21546</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>44203</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>31811</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>32611</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>61518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>283</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>212460</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>201983</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>414444</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>188088</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>183463</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>388238</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>230217</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>218489</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>444656</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>75790</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>57527</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>133316</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>64509</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>47698</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>119359</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>86295</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>69086</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>149925</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>416</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>405</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>314265</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>286459</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>600724</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>289722</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>265055</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>566496</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>339438</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>307741</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>633926</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>